--- a/artfynd/A 5130-2025 artfynd.xlsx
+++ b/artfynd/A 5130-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122664433</v>
+        <v>122664323</v>
       </c>
       <c r="B3" t="n">
-        <v>57384</v>
+        <v>57400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,16 +803,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -828,14 +828,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bastudalen, Bastudalen, Ång</t>
+          <t>Hemsjön, Hemsjön, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584123</v>
+        <v>583930</v>
       </c>
       <c r="R3" t="n">
-        <v>7051703</v>
+        <v>7051784</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:40</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122664023</v>
+        <v>122664433</v>
       </c>
       <c r="B4" t="n">
-        <v>79738</v>
+        <v>57384</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,34 +920,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Åstjärnmyran, Åstjärnmyran, Ång</t>
+          <t>Bastudalen, Bastudalen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584237</v>
+        <v>584123</v>
       </c>
       <c r="R4" t="n">
-        <v>7051847</v>
+        <v>7051703</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +994,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122665036</v>
+        <v>122664023</v>
       </c>
       <c r="B5" t="n">
-        <v>57384</v>
+        <v>79738</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,39 +1042,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hemsjön, Hemsjön, Ång</t>
+          <t>Åstjärnmyran, Åstjärnmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584035</v>
+        <v>584237</v>
       </c>
       <c r="R5" t="n">
-        <v>7051747</v>
+        <v>7051847</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,12 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:19</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,22 +1126,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122664323</v>
+        <v>122665036</v>
       </c>
       <c r="B6" t="n">
-        <v>57400</v>
+        <v>57384</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,16 +1154,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1179,7 +1174,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1188,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583930</v>
+        <v>584035</v>
       </c>
       <c r="R6" t="n">
-        <v>7051784</v>
+        <v>7051747</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1223,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1233,7 +1228,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,22 +1248,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122663601</v>
+        <v>122663837</v>
       </c>
       <c r="B7" t="n">
-        <v>57384</v>
+        <v>78657</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,39 +1276,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bastudalen, Bastudalen, Ång</t>
+          <t>Åstjärnmyran, Åstjärnmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584198</v>
+        <v>584291</v>
       </c>
       <c r="R7" t="n">
-        <v>7051691</v>
+        <v>7051801</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1340,7 +1335,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1350,12 +1345,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1504,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122663837</v>
+        <v>122663601</v>
       </c>
       <c r="B9" t="n">
-        <v>78657</v>
+        <v>57384</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1520,34 +1510,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Åstjärnmyran, Åstjärnmyran, Ång</t>
+          <t>Bastudalen, Bastudalen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584291</v>
+        <v>584198</v>
       </c>
       <c r="R9" t="n">
-        <v>7051801</v>
+        <v>7051691</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1579,7 +1574,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1589,7 +1584,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 5130-2025 artfynd.xlsx
+++ b/artfynd/A 5130-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122663802</v>
+        <v>122663837</v>
       </c>
       <c r="B2" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584277</v>
+        <v>584291</v>
       </c>
       <c r="R2" t="n">
-        <v>7051732</v>
+        <v>7051801</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,12 +775,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122664433</v>
+        <v>122664023</v>
       </c>
       <c r="B4" t="n">
-        <v>57384</v>
+        <v>79741</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,39 +920,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bastudalen, Bastudalen, Ång</t>
+          <t>Åstjärnmyran, Åstjärnmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584123</v>
+        <v>584237</v>
       </c>
       <c r="R4" t="n">
-        <v>7051703</v>
+        <v>7051847</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,12 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:40</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122664023</v>
+        <v>122664433</v>
       </c>
       <c r="B5" t="n">
-        <v>79738</v>
+        <v>57384</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,34 +1032,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Åstjärnmyran, Åstjärnmyran, Ång</t>
+          <t>Bastudalen, Bastudalen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584237</v>
+        <v>584123</v>
       </c>
       <c r="R5" t="n">
-        <v>7051847</v>
+        <v>7051703</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1106,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,7 +1138,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122665036</v>
+        <v>122663601</v>
       </c>
       <c r="B6" t="n">
         <v>57384</v>
@@ -1174,19 +1174,19 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hemsjön, Hemsjön, Ång</t>
+          <t>Bastudalen, Bastudalen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584035</v>
+        <v>584198</v>
       </c>
       <c r="R6" t="n">
-        <v>7051747</v>
+        <v>7051691</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,22 +1248,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122663837</v>
+        <v>122664446</v>
       </c>
       <c r="B7" t="n">
-        <v>78657</v>
+        <v>57384</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,34 +1276,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Åstjärnmyran, Åstjärnmyran, Ång</t>
+          <t>Bastudalen, Bastudalen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584291</v>
+        <v>584139</v>
       </c>
       <c r="R7" t="n">
-        <v>7051801</v>
+        <v>7051693</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,7 +1340,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1345,7 +1350,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,19 +1370,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122664446</v>
+        <v>122665036</v>
       </c>
       <c r="B8" t="n">
         <v>57384</v>
@@ -1408,19 +1418,19 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bastudalen, Bastudalen, Ång</t>
+          <t>Hemsjön, Hemsjön, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584139</v>
+        <v>584035</v>
       </c>
       <c r="R8" t="n">
-        <v>7051693</v>
+        <v>7051747</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,7 +1462,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1462,7 +1472,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1494,10 +1504,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122663601</v>
+        <v>122663802</v>
       </c>
       <c r="B9" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,39 +1520,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bastudalen, Bastudalen, Ång</t>
+          <t>Åstjärnmyran, Åstjärnmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584198</v>
+        <v>584277</v>
       </c>
       <c r="R9" t="n">
-        <v>7051691</v>
+        <v>7051732</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1574,7 +1579,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1584,12 +1589,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1604,12 +1604,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 5130-2025 artfynd.xlsx
+++ b/artfynd/A 5130-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122664323</v>
+        <v>122665036</v>
       </c>
       <c r="B3" t="n">
-        <v>57400</v>
+        <v>57384</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,16 +803,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -823,7 +823,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583930</v>
+        <v>584035</v>
       </c>
       <c r="R3" t="n">
-        <v>7051784</v>
+        <v>7051747</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,22 +897,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122664023</v>
+        <v>122664446</v>
       </c>
       <c r="B4" t="n">
-        <v>79741</v>
+        <v>57384</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,34 +925,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Åstjärnmyran, Åstjärnmyran, Ång</t>
+          <t>Bastudalen, Bastudalen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584237</v>
+        <v>584139</v>
       </c>
       <c r="R4" t="n">
-        <v>7051847</v>
+        <v>7051693</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +999,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,19 +1019,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122664433</v>
+        <v>122663601</v>
       </c>
       <c r="B5" t="n">
         <v>57384</v>
@@ -1061,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584123</v>
+        <v>584198</v>
       </c>
       <c r="R5" t="n">
-        <v>7051703</v>
+        <v>7051691</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,12 +1121,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,10 +1153,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122663601</v>
+        <v>122664323</v>
       </c>
       <c r="B6" t="n">
-        <v>57384</v>
+        <v>57400</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,16 +1169,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1179,14 +1194,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bastudalen, Bastudalen, Ång</t>
+          <t>Hemsjön, Hemsjön, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584198</v>
+        <v>583930</v>
       </c>
       <c r="R6" t="n">
-        <v>7051691</v>
+        <v>7051784</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,12 +1243,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122664446</v>
+        <v>122664023</v>
       </c>
       <c r="B7" t="n">
-        <v>57384</v>
+        <v>79741</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,39 +1286,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bastudalen, Bastudalen, Ång</t>
+          <t>Åstjärnmyran, Åstjärnmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584139</v>
+        <v>584237</v>
       </c>
       <c r="R7" t="n">
-        <v>7051693</v>
+        <v>7051847</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1340,7 +1345,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1350,12 +1355,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:38</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1370,19 +1370,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122665036</v>
+        <v>122664433</v>
       </c>
       <c r="B8" t="n">
         <v>57384</v>
@@ -1418,19 +1418,19 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hemsjön, Hemsjön, Ång</t>
+          <t>Bastudalen, Bastudalen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584035</v>
+        <v>584123</v>
       </c>
       <c r="R8" t="n">
-        <v>7051747</v>
+        <v>7051703</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1472,12 +1472,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1492,12 +1492,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 5130-2025 artfynd.xlsx
+++ b/artfynd/A 5130-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122664023</v>
+        <v>122663837</v>
       </c>
       <c r="B2" t="n">
-        <v>79843</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584237</v>
+        <v>584291</v>
       </c>
       <c r="R2" t="n">
-        <v>7051847</v>
+        <v>7051801</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122663837</v>
+        <v>122663601</v>
       </c>
       <c r="B3" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Åstjärnmyran, Åstjärnmyran, Ång</t>
+          <t>Bastudalen, Bastudalen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584291</v>
+        <v>584198</v>
       </c>
       <c r="R3" t="n">
-        <v>7051801</v>
+        <v>7051691</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122663802</v>
+        <v>122664446</v>
       </c>
       <c r="B4" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,34 +925,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Åstjärnmyran, Åstjärnmyran, Ång</t>
+          <t>Bastudalen, Bastudalen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584277</v>
+        <v>584139</v>
       </c>
       <c r="R4" t="n">
-        <v>7051732</v>
+        <v>7051693</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +999,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122665036</v>
+        <v>122663802</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,39 +1047,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hemsjön, Hemsjön, Ång</t>
+          <t>Åstjärnmyran, Åstjärnmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584035</v>
+        <v>584277</v>
       </c>
       <c r="R5" t="n">
-        <v>7051747</v>
+        <v>7051732</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,12 +1116,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:19</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1255,7 +1265,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122664446</v>
+        <v>122665036</v>
       </c>
       <c r="B7" t="n">
         <v>57478</v>
@@ -1291,19 +1301,19 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bastudalen, Bastudalen, Ång</t>
+          <t>Hemsjön, Hemsjön, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584139</v>
+        <v>584035</v>
       </c>
       <c r="R7" t="n">
-        <v>7051693</v>
+        <v>7051747</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,7 +1345,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1345,7 +1355,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1377,10 +1387,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122664323</v>
+        <v>122664023</v>
       </c>
       <c r="B8" t="n">
-        <v>57494</v>
+        <v>79847</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1393,39 +1403,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hemsjön, Hemsjön, Ång</t>
+          <t>Åstjärnmyran, Åstjärnmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583930</v>
+        <v>584237</v>
       </c>
       <c r="R8" t="n">
-        <v>7051784</v>
+        <v>7051847</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1457,7 +1462,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1467,7 +1472,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1494,10 +1499,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122663601</v>
+        <v>122664323</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,16 +1515,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1535,14 +1540,14 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bastudalen, Bastudalen, Ång</t>
+          <t>Hemsjön, Hemsjön, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584198</v>
+        <v>583930</v>
       </c>
       <c r="R9" t="n">
-        <v>7051691</v>
+        <v>7051784</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1574,7 +1579,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1584,12 +1589,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 5130-2025 artfynd.xlsx
+++ b/artfynd/A 5130-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122663837</v>
+        <v>122663802</v>
       </c>
       <c r="B2" t="n">
         <v>78766</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584291</v>
+        <v>584277</v>
       </c>
       <c r="R2" t="n">
-        <v>7051801</v>
+        <v>7051732</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122663601</v>
+        <v>122664323</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,16 +803,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -828,14 +828,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bastudalen, Bastudalen, Ång</t>
+          <t>Hemsjön, Hemsjön, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584198</v>
+        <v>583930</v>
       </c>
       <c r="R3" t="n">
-        <v>7051691</v>
+        <v>7051784</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122664446</v>
+        <v>122664023</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,39 +920,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bastudalen, Bastudalen, Ång</t>
+          <t>Åstjärnmyran, Åstjärnmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584139</v>
+        <v>584237</v>
       </c>
       <c r="R4" t="n">
-        <v>7051693</v>
+        <v>7051847</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,12 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:38</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,22 +1004,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122663802</v>
+        <v>122664433</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,34 +1032,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Åstjärnmyran, Åstjärnmyran, Ång</t>
+          <t>Bastudalen, Bastudalen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584277</v>
+        <v>584123</v>
       </c>
       <c r="R5" t="n">
-        <v>7051732</v>
+        <v>7051703</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,7 +1106,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,22 +1126,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122664433</v>
+        <v>122663837</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,39 +1154,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bastudalen, Bastudalen, Ång</t>
+          <t>Åstjärnmyran, Åstjärnmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584123</v>
+        <v>584291</v>
       </c>
       <c r="R6" t="n">
-        <v>7051703</v>
+        <v>7051801</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1223,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1233,12 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:40</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1265,7 +1250,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122665036</v>
+        <v>122663601</v>
       </c>
       <c r="B7" t="n">
         <v>57478</v>
@@ -1301,19 +1286,19 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hemsjön, Hemsjön, Ång</t>
+          <t>Bastudalen, Bastudalen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584035</v>
+        <v>584198</v>
       </c>
       <c r="R7" t="n">
-        <v>7051747</v>
+        <v>7051691</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1355,12 +1340,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1375,22 +1360,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122664023</v>
+        <v>122664446</v>
       </c>
       <c r="B8" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1403,34 +1388,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Åstjärnmyran, Åstjärnmyran, Ång</t>
+          <t>Bastudalen, Bastudalen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584237</v>
+        <v>584139</v>
       </c>
       <c r="R8" t="n">
-        <v>7051847</v>
+        <v>7051693</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1462,7 +1452,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1472,7 +1462,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,22 +1482,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122664323</v>
+        <v>122665036</v>
       </c>
       <c r="B9" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1515,16 +1510,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1535,7 +1530,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1544,10 +1539,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583930</v>
+        <v>584035</v>
       </c>
       <c r="R9" t="n">
-        <v>7051784</v>
+        <v>7051747</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1579,7 +1574,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1589,7 +1584,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1604,12 +1604,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 5130-2025 artfynd.xlsx
+++ b/artfynd/A 5130-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122663802</v>
+        <v>122664433</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Åstjärnmyran, Åstjärnmyran, Ång</t>
+          <t>Bastudalen, Bastudalen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584277</v>
+        <v>584123</v>
       </c>
       <c r="R2" t="n">
-        <v>7051732</v>
+        <v>7051703</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,12 +785,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -904,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122664023</v>
+        <v>122664446</v>
       </c>
       <c r="B4" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,34 +930,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Åstjärnmyran, Åstjärnmyran, Ång</t>
+          <t>Bastudalen, Bastudalen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584237</v>
+        <v>584139</v>
       </c>
       <c r="R4" t="n">
-        <v>7051847</v>
+        <v>7051693</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +1004,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,19 +1024,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122664433</v>
+        <v>122663601</v>
       </c>
       <c r="B5" t="n">
         <v>57478</v>
@@ -1061,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584123</v>
+        <v>584198</v>
       </c>
       <c r="R5" t="n">
-        <v>7051703</v>
+        <v>7051691</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1116,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,12 +1126,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,7 +1158,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122663837</v>
+        <v>122663802</v>
       </c>
       <c r="B6" t="n">
         <v>78766</v>
@@ -1178,10 +1198,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584291</v>
+        <v>584277</v>
       </c>
       <c r="R6" t="n">
-        <v>7051801</v>
+        <v>7051732</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1243,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,19 +1258,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122663601</v>
+        <v>122665036</v>
       </c>
       <c r="B7" t="n">
         <v>57478</v>
@@ -1286,19 +1306,19 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bastudalen, Bastudalen, Ång</t>
+          <t>Hemsjön, Hemsjön, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584198</v>
+        <v>584035</v>
       </c>
       <c r="R7" t="n">
-        <v>7051691</v>
+        <v>7051747</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,7 +1350,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,12 +1360,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,22 +1380,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122664446</v>
+        <v>122664023</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,39 +1408,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bastudalen, Bastudalen, Ång</t>
+          <t>Åstjärnmyran, Åstjärnmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584139</v>
+        <v>584237</v>
       </c>
       <c r="R8" t="n">
-        <v>7051693</v>
+        <v>7051847</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,7 +1467,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1462,12 +1477,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:38</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,22 +1492,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122665036</v>
+        <v>122663837</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,39 +1520,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hemsjön, Hemsjön, Ång</t>
+          <t>Åstjärnmyran, Åstjärnmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584035</v>
+        <v>584291</v>
       </c>
       <c r="R9" t="n">
-        <v>7051747</v>
+        <v>7051801</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1574,7 +1579,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1584,12 +1589,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:19</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1604,12 +1604,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 5130-2025 artfynd.xlsx
+++ b/artfynd/A 5130-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122664433</v>
+        <v>122664323</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -716,14 +716,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bastudalen, Bastudalen, Ång</t>
+          <t>Hemsjön, Hemsjön, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584123</v>
+        <v>583930</v>
       </c>
       <c r="R2" t="n">
-        <v>7051703</v>
+        <v>7051784</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:40</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122664323</v>
+        <v>122664433</v>
       </c>
       <c r="B3" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,16 +808,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -838,14 +833,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hemsjön, Hemsjön, Ång</t>
+          <t>Bastudalen, Bastudalen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583930</v>
+        <v>584123</v>
       </c>
       <c r="R3" t="n">
-        <v>7051784</v>
+        <v>7051703</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +882,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 5130-2025 artfynd.xlsx
+++ b/artfynd/A 5130-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122664323</v>
+        <v>122664433</v>
       </c>
       <c r="B2" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -716,14 +716,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hemsjön, Hemsjön, Ång</t>
+          <t>Bastudalen, Bastudalen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583930</v>
+        <v>584123</v>
       </c>
       <c r="R2" t="n">
-        <v>7051784</v>
+        <v>7051703</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122664433</v>
+        <v>122664323</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,16 +813,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -833,14 +838,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bastudalen, Bastudalen, Ång</t>
+          <t>Hemsjön, Hemsjön, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584123</v>
+        <v>583930</v>
       </c>
       <c r="R3" t="n">
-        <v>7051703</v>
+        <v>7051784</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,12 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:40</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 5130-2025 artfynd.xlsx
+++ b/artfynd/A 5130-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122664433</v>
+        <v>122664323</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -716,14 +716,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bastudalen, Bastudalen, Ång</t>
+          <t>Hemsjön, Hemsjön, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584123</v>
+        <v>583930</v>
       </c>
       <c r="R2" t="n">
-        <v>7051703</v>
+        <v>7051784</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:40</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122664323</v>
+        <v>122663802</v>
       </c>
       <c r="B3" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,39 +808,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hemsjön, Hemsjön, Ång</t>
+          <t>Åstjärnmyran, Åstjärnmyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583930</v>
+        <v>584277</v>
       </c>
       <c r="R3" t="n">
-        <v>7051784</v>
+        <v>7051732</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,22 +892,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122664446</v>
+        <v>122664023</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,39 +920,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bastudalen, Bastudalen, Ång</t>
+          <t>Åstjärnmyran, Åstjärnmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584139</v>
+        <v>584237</v>
       </c>
       <c r="R4" t="n">
-        <v>7051693</v>
+        <v>7051847</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,12 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:38</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,19 +1004,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122663601</v>
+        <v>122664433</v>
       </c>
       <c r="B5" t="n">
         <v>57478</v>
@@ -1081,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584198</v>
+        <v>584123</v>
       </c>
       <c r="R5" t="n">
-        <v>7051691</v>
+        <v>7051703</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1116,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1126,12 +1106,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1158,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122663802</v>
+        <v>122663601</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1174,34 +1154,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Åstjärnmyran, Åstjärnmyran, Ång</t>
+          <t>Bastudalen, Bastudalen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584277</v>
+        <v>584198</v>
       </c>
       <c r="R6" t="n">
-        <v>7051732</v>
+        <v>7051691</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,7 +1228,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,12 +1248,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1392,10 +1382,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122664023</v>
+        <v>122663837</v>
       </c>
       <c r="B8" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1408,21 +1398,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1432,10 +1422,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584237</v>
+        <v>584291</v>
       </c>
       <c r="R8" t="n">
-        <v>7051847</v>
+        <v>7051801</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1467,7 +1457,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1477,7 +1467,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1504,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122663837</v>
+        <v>122664446</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1520,34 +1510,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Åstjärnmyran, Åstjärnmyran, Ång</t>
+          <t>Bastudalen, Bastudalen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584291</v>
+        <v>584139</v>
       </c>
       <c r="R9" t="n">
-        <v>7051801</v>
+        <v>7051693</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1579,7 +1574,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1589,7 +1584,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1604,12 +1604,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 5130-2025 artfynd.xlsx
+++ b/artfynd/A 5130-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122664323</v>
+        <v>122663837</v>
       </c>
       <c r="B2" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hemsjön, Hemsjön, Ång</t>
+          <t>Åstjärnmyran, Åstjärnmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583930</v>
+        <v>584291</v>
       </c>
       <c r="R2" t="n">
-        <v>7051784</v>
+        <v>7051801</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -904,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122664023</v>
+        <v>122663601</v>
       </c>
       <c r="B4" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,34 +915,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Åstjärnmyran, Åstjärnmyran, Ång</t>
+          <t>Bastudalen, Bastudalen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584237</v>
+        <v>584198</v>
       </c>
       <c r="R4" t="n">
-        <v>7051847</v>
+        <v>7051691</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,7 +1021,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122664433</v>
+        <v>122664446</v>
       </c>
       <c r="B5" t="n">
         <v>57478</v>
@@ -1061,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584123</v>
+        <v>584139</v>
       </c>
       <c r="R5" t="n">
-        <v>7051703</v>
+        <v>7051693</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,12 +1111,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,19 +1131,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122663601</v>
+        <v>122665036</v>
       </c>
       <c r="B6" t="n">
         <v>57478</v>
@@ -1174,19 +1179,19 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bastudalen, Bastudalen, Ång</t>
+          <t>Hemsjön, Hemsjön, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584198</v>
+        <v>584035</v>
       </c>
       <c r="R6" t="n">
-        <v>7051691</v>
+        <v>7051747</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,7 +1223,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,12 +1233,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,22 +1253,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122665036</v>
+        <v>122664323</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,16 +1281,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1296,7 +1301,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1305,10 +1310,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584035</v>
+        <v>583930</v>
       </c>
       <c r="R7" t="n">
-        <v>7051747</v>
+        <v>7051784</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1340,7 +1345,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1350,12 +1355,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:19</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1370,22 +1370,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122663837</v>
+        <v>122664433</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1398,34 +1398,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Åstjärnmyran, Åstjärnmyran, Ång</t>
+          <t>Bastudalen, Bastudalen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584291</v>
+        <v>584123</v>
       </c>
       <c r="R8" t="n">
-        <v>7051801</v>
+        <v>7051703</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1457,7 +1462,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1467,7 +1472,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1494,10 +1504,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122664446</v>
+        <v>122664023</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,39 +1520,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bastudalen, Bastudalen, Ång</t>
+          <t>Åstjärnmyran, Åstjärnmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584139</v>
+        <v>584237</v>
       </c>
       <c r="R9" t="n">
-        <v>7051693</v>
+        <v>7051847</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1574,7 +1579,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1584,12 +1589,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:38</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1604,12 +1604,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 5130-2025 artfynd.xlsx
+++ b/artfynd/A 5130-2025 artfynd.xlsx
@@ -1265,10 +1265,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122664323</v>
+        <v>122664433</v>
       </c>
       <c r="B7" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1281,16 +1281,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1306,14 +1306,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hemsjön, Hemsjön, Ång</t>
+          <t>Bastudalen, Bastudalen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583930</v>
+        <v>584123</v>
       </c>
       <c r="R7" t="n">
-        <v>7051784</v>
+        <v>7051703</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1355,7 +1355,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1382,10 +1387,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122664433</v>
+        <v>122664323</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1398,16 +1403,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1423,14 +1428,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bastudalen, Bastudalen, Ång</t>
+          <t>Hemsjön, Hemsjön, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584123</v>
+        <v>583930</v>
       </c>
       <c r="R8" t="n">
-        <v>7051703</v>
+        <v>7051784</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1462,7 +1467,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1472,12 +1477,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:40</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 5130-2025 artfynd.xlsx
+++ b/artfynd/A 5130-2025 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122663601</v>
+        <v>122664323</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,16 +915,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -940,14 +940,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bastudalen, Bastudalen, Ång</t>
+          <t>Hemsjön, Hemsjön, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584198</v>
+        <v>583930</v>
       </c>
       <c r="R4" t="n">
-        <v>7051691</v>
+        <v>7051784</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,12 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,7 +1016,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122664446</v>
+        <v>122664433</v>
       </c>
       <c r="B5" t="n">
         <v>57478</v>
@@ -1066,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584139</v>
+        <v>584123</v>
       </c>
       <c r="R5" t="n">
-        <v>7051693</v>
+        <v>7051703</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,12 +1106,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,22 +1126,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122665036</v>
+        <v>122664023</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,39 +1154,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hemsjön, Hemsjön, Ång</t>
+          <t>Åstjärnmyran, Åstjärnmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584035</v>
+        <v>584237</v>
       </c>
       <c r="R6" t="n">
-        <v>7051747</v>
+        <v>7051847</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1223,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1233,12 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:19</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,19 +1238,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122664433</v>
+        <v>122663601</v>
       </c>
       <c r="B7" t="n">
         <v>57478</v>
@@ -1310,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584123</v>
+        <v>584198</v>
       </c>
       <c r="R7" t="n">
-        <v>7051703</v>
+        <v>7051691</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1355,12 +1340,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1387,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122664323</v>
+        <v>122665036</v>
       </c>
       <c r="B8" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1403,16 +1388,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1423,7 +1408,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1432,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583930</v>
+        <v>584035</v>
       </c>
       <c r="R8" t="n">
-        <v>7051784</v>
+        <v>7051747</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1467,7 +1452,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1477,7 +1462,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1492,22 +1482,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122664023</v>
+        <v>122664446</v>
       </c>
       <c r="B9" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1520,34 +1510,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Åstjärnmyran, Åstjärnmyran, Ång</t>
+          <t>Bastudalen, Bastudalen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584237</v>
+        <v>584139</v>
       </c>
       <c r="R9" t="n">
-        <v>7051847</v>
+        <v>7051693</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1579,7 +1574,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1589,7 +1584,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1604,12 +1604,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 5130-2025 artfynd.xlsx
+++ b/artfynd/A 5130-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122663837</v>
+        <v>122664023</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584291</v>
+        <v>584237</v>
       </c>
       <c r="R2" t="n">
-        <v>7051801</v>
+        <v>7051847</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122663802</v>
+        <v>122664433</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Åstjärnmyran, Åstjärnmyran, Ång</t>
+          <t>Bastudalen, Bastudalen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584277</v>
+        <v>584123</v>
       </c>
       <c r="R3" t="n">
-        <v>7051732</v>
+        <v>7051703</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,12 +897,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1016,7 +1026,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122664433</v>
+        <v>122665036</v>
       </c>
       <c r="B5" t="n">
         <v>57478</v>
@@ -1052,19 +1062,19 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bastudalen, Bastudalen, Ång</t>
+          <t>Hemsjön, Hemsjön, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584123</v>
+        <v>584035</v>
       </c>
       <c r="R5" t="n">
-        <v>7051703</v>
+        <v>7051747</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,12 +1116,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,22 +1136,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122664023</v>
+        <v>122664446</v>
       </c>
       <c r="B6" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,34 +1164,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Åstjärnmyran, Åstjärnmyran, Ång</t>
+          <t>Bastudalen, Bastudalen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584237</v>
+        <v>584139</v>
       </c>
       <c r="R6" t="n">
-        <v>7051847</v>
+        <v>7051693</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1228,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1238,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,22 +1258,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122663601</v>
+        <v>122663837</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,39 +1286,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bastudalen, Bastudalen, Ång</t>
+          <t>Åstjärnmyran, Åstjärnmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584198</v>
+        <v>584291</v>
       </c>
       <c r="R7" t="n">
-        <v>7051691</v>
+        <v>7051801</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,7 +1345,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,12 +1355,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1372,7 +1382,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122665036</v>
+        <v>122663601</v>
       </c>
       <c r="B8" t="n">
         <v>57478</v>
@@ -1408,19 +1418,19 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hemsjön, Hemsjön, Ång</t>
+          <t>Bastudalen, Bastudalen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584035</v>
+        <v>584198</v>
       </c>
       <c r="R8" t="n">
-        <v>7051747</v>
+        <v>7051691</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,7 +1462,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1462,12 +1472,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,22 +1492,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122664446</v>
+        <v>122663802</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,39 +1520,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bastudalen, Bastudalen, Ång</t>
+          <t>Åstjärnmyran, Åstjärnmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584139</v>
+        <v>584277</v>
       </c>
       <c r="R9" t="n">
-        <v>7051693</v>
+        <v>7051732</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1574,7 +1579,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1584,12 +1589,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:38</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 5130-2025 artfynd.xlsx
+++ b/artfynd/A 5130-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122664023</v>
+        <v>122663837</v>
       </c>
       <c r="B2" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584237</v>
+        <v>584291</v>
       </c>
       <c r="R2" t="n">
-        <v>7051847</v>
+        <v>7051801</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122664433</v>
+        <v>122664446</v>
       </c>
       <c r="B3" t="n">
         <v>57478</v>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584123</v>
+        <v>584139</v>
       </c>
       <c r="R3" t="n">
-        <v>7051703</v>
+        <v>7051693</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,22 +897,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122664323</v>
+        <v>122665036</v>
       </c>
       <c r="B4" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,16 +925,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -945,7 +945,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583930</v>
+        <v>584035</v>
       </c>
       <c r="R4" t="n">
-        <v>7051784</v>
+        <v>7051747</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +999,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,19 +1019,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122665036</v>
+        <v>122663601</v>
       </c>
       <c r="B5" t="n">
         <v>57478</v>
@@ -1062,19 +1067,19 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hemsjön, Hemsjön, Ång</t>
+          <t>Bastudalen, Bastudalen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584035</v>
+        <v>584198</v>
       </c>
       <c r="R5" t="n">
-        <v>7051747</v>
+        <v>7051691</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,12 +1121,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,22 +1141,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122664446</v>
+        <v>122664323</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1164,16 +1169,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1189,14 +1194,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bastudalen, Bastudalen, Ång</t>
+          <t>Hemsjön, Hemsjön, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584139</v>
+        <v>583930</v>
       </c>
       <c r="R6" t="n">
-        <v>7051693</v>
+        <v>7051784</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1228,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1238,12 +1243,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:38</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,22 +1258,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122663837</v>
+        <v>122664023</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1286,21 +1286,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584291</v>
+        <v>584237</v>
       </c>
       <c r="R7" t="n">
-        <v>7051801</v>
+        <v>7051847</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1382,7 +1382,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122663601</v>
+        <v>122664433</v>
       </c>
       <c r="B8" t="n">
         <v>57478</v>
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584198</v>
+        <v>584123</v>
       </c>
       <c r="R8" t="n">
-        <v>7051691</v>
+        <v>7051703</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1472,12 +1472,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 5130-2025 artfynd.xlsx
+++ b/artfynd/A 5130-2025 artfynd.xlsx
@@ -1616,10 +1616,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123547701</v>
+        <v>123546445</v>
       </c>
       <c r="B10" t="n">
-        <v>98379</v>
+        <v>57503</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1628,42 +1628,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>25</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hemsjön, Hemsjön, Ång</t>
+          <t>Åstjärnmyran, Åstjärnmyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>584105</v>
+        <v>584230</v>
       </c>
       <c r="R10" t="n">
-        <v>7051736</v>
+        <v>7051782</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1695,7 +1696,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1705,7 +1706,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1720,22 +1721,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123546109</v>
+        <v>123547701</v>
       </c>
       <c r="B11" t="n">
-        <v>79856</v>
+        <v>98396</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1744,38 +1745,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bastudalen, Bastudalen, Ång</t>
+          <t>Hemsjön, Hemsjön, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>584186</v>
+        <v>584105</v>
       </c>
       <c r="R11" t="n">
-        <v>7051726</v>
+        <v>7051736</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1807,7 +1812,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1817,7 +1822,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1832,22 +1837,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123546445</v>
+        <v>123546109</v>
       </c>
       <c r="B12" t="n">
-        <v>57497</v>
+        <v>79862</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1860,39 +1865,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Åstjärnmyran, Åstjärnmyran, Ång</t>
+          <t>Bastudalen, Bastudalen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>584230</v>
+        <v>584186</v>
       </c>
       <c r="R12" t="n">
-        <v>7051782</v>
+        <v>7051726</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 5130-2025 artfynd.xlsx
+++ b/artfynd/A 5130-2025 artfynd.xlsx
@@ -1619,7 +1619,7 @@
         <v>123546445</v>
       </c>
       <c r="B10" t="n">
-        <v>57503</v>
+        <v>57506</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1733,10 +1733,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123547701</v>
+        <v>123546109</v>
       </c>
       <c r="B11" t="n">
-        <v>98396</v>
+        <v>79867</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1745,42 +1745,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hemsjön, Hemsjön, Ång</t>
+          <t>Bastudalen, Bastudalen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>584105</v>
+        <v>584186</v>
       </c>
       <c r="R11" t="n">
-        <v>7051736</v>
+        <v>7051726</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1812,7 +1808,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1822,7 +1818,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1837,22 +1833,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123546109</v>
+        <v>123547701</v>
       </c>
       <c r="B12" t="n">
-        <v>79862</v>
+        <v>98502</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1861,38 +1857,42 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bastudalen, Bastudalen, Ång</t>
+          <t>Hemsjön, Hemsjön, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>584186</v>
+        <v>584105</v>
       </c>
       <c r="R12" t="n">
-        <v>7051726</v>
+        <v>7051736</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1949,12 +1949,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 5130-2025 artfynd.xlsx
+++ b/artfynd/A 5130-2025 artfynd.xlsx
@@ -1619,7 +1619,7 @@
         <v>123546445</v>
       </c>
       <c r="B10" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1733,10 +1733,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123546109</v>
+        <v>123547701</v>
       </c>
       <c r="B11" t="n">
-        <v>79867</v>
+        <v>98504</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1745,38 +1745,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bastudalen, Bastudalen, Ång</t>
+          <t>Hemsjön, Hemsjön, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>584186</v>
+        <v>584105</v>
       </c>
       <c r="R11" t="n">
-        <v>7051726</v>
+        <v>7051736</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1808,7 +1812,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1818,7 +1822,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1833,22 +1837,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123547701</v>
+        <v>123546109</v>
       </c>
       <c r="B12" t="n">
-        <v>98502</v>
+        <v>79869</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1857,42 +1861,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hemsjön, Hemsjön, Ång</t>
+          <t>Bastudalen, Bastudalen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>584105</v>
+        <v>584186</v>
       </c>
       <c r="R12" t="n">
-        <v>7051736</v>
+        <v>7051726</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1949,12 +1949,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 5130-2025 artfynd.xlsx
+++ b/artfynd/A 5130-2025 artfynd.xlsx
@@ -1616,10 +1616,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123546445</v>
+        <v>123547701</v>
       </c>
       <c r="B10" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1628,43 +1628,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>25</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Åstjärnmyran, Åstjärnmyran, Ång</t>
+          <t>Hemsjön, Hemsjön, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>584230</v>
+        <v>584105</v>
       </c>
       <c r="R10" t="n">
-        <v>7051782</v>
+        <v>7051736</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1696,7 +1695,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1706,7 +1705,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1721,22 +1720,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123547701</v>
+        <v>123546445</v>
       </c>
       <c r="B11" t="n">
-        <v>98504</v>
+        <v>57507</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1745,42 +1744,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>25</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hemsjön, Hemsjön, Ång</t>
+          <t>Åstjärnmyran, Åstjärnmyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>584105</v>
+        <v>584230</v>
       </c>
       <c r="R11" t="n">
-        <v>7051736</v>
+        <v>7051782</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1812,7 +1812,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1837,12 +1837,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 5130-2025 artfynd.xlsx
+++ b/artfynd/A 5130-2025 artfynd.xlsx
@@ -1616,10 +1616,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123547701</v>
+        <v>123546109</v>
       </c>
       <c r="B10" t="n">
-        <v>98079</v>
+        <v>79869</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1628,42 +1628,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hemsjön, Hemsjön, Ång</t>
+          <t>Bastudalen, Bastudalen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>584105</v>
+        <v>584186</v>
       </c>
       <c r="R10" t="n">
-        <v>7051736</v>
+        <v>7051726</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1695,7 +1691,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1705,7 +1701,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1720,22 +1716,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123546445</v>
+        <v>123547701</v>
       </c>
       <c r="B11" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1744,43 +1740,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>25</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Åstjärnmyran, Åstjärnmyran, Ång</t>
+          <t>Hemsjön, Hemsjön, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>584230</v>
+        <v>584105</v>
       </c>
       <c r="R11" t="n">
-        <v>7051782</v>
+        <v>7051736</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1812,7 +1807,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1822,7 +1817,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1837,22 +1832,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123546109</v>
+        <v>123546445</v>
       </c>
       <c r="B12" t="n">
-        <v>79869</v>
+        <v>57507</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1865,34 +1860,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bastudalen, Bastudalen, Ång</t>
+          <t>Åstjärnmyran, Åstjärnmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>584186</v>
+        <v>584230</v>
       </c>
       <c r="R12" t="n">
-        <v>7051726</v>
+        <v>7051782</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 5130-2025 artfynd.xlsx
+++ b/artfynd/A 5130-2025 artfynd.xlsx
@@ -1616,10 +1616,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123546109</v>
+        <v>123546445</v>
       </c>
       <c r="B10" t="n">
-        <v>79869</v>
+        <v>57507</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1632,34 +1632,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bastudalen, Bastudalen, Ång</t>
+          <t>Åstjärnmyran, Åstjärnmyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>584186</v>
+        <v>584230</v>
       </c>
       <c r="R10" t="n">
-        <v>7051726</v>
+        <v>7051782</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1691,7 +1696,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1701,7 +1706,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1844,10 +1849,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123546445</v>
+        <v>123546109</v>
       </c>
       <c r="B12" t="n">
-        <v>57507</v>
+        <v>79869</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1860,39 +1865,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Åstjärnmyran, Åstjärnmyran, Ång</t>
+          <t>Bastudalen, Bastudalen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>584230</v>
+        <v>584186</v>
       </c>
       <c r="R12" t="n">
-        <v>7051782</v>
+        <v>7051726</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 5130-2025 artfynd.xlsx
+++ b/artfynd/A 5130-2025 artfynd.xlsx
@@ -1616,10 +1616,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123546445</v>
+        <v>123547701</v>
       </c>
       <c r="B10" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1628,43 +1628,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>25</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Åstjärnmyran, Åstjärnmyran, Ång</t>
+          <t>Hemsjön, Hemsjön, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>584230</v>
+        <v>584105</v>
       </c>
       <c r="R10" t="n">
-        <v>7051782</v>
+        <v>7051736</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1696,7 +1695,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1706,7 +1705,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1721,22 +1720,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123547701</v>
+        <v>123546109</v>
       </c>
       <c r="B11" t="n">
-        <v>98079</v>
+        <v>79869</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1745,42 +1744,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hemsjön, Hemsjön, Ång</t>
+          <t>Bastudalen, Bastudalen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>584105</v>
+        <v>584186</v>
       </c>
       <c r="R11" t="n">
-        <v>7051736</v>
+        <v>7051726</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1812,7 +1807,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1822,7 +1817,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1837,22 +1832,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123546109</v>
+        <v>123546445</v>
       </c>
       <c r="B12" t="n">
-        <v>79869</v>
+        <v>57507</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1865,34 +1860,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bastudalen, Bastudalen, Ång</t>
+          <t>Åstjärnmyran, Åstjärnmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>584186</v>
+        <v>584230</v>
       </c>
       <c r="R12" t="n">
-        <v>7051726</v>
+        <v>7051782</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD12" t="b">
